--- a/product_upload/packages/48/file.xlsx
+++ b/product_upload/packages/48/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Sayen</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-33674933A0B1</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Sayen</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-38866EA056A9</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1208,6 +1223,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Nosco</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-5294F3289D84</t>
         </is>
       </c>
@@ -1231,7 +1251,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1394,6 +1414,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Apriva</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-99359518EDA7</t>
         </is>
       </c>
@@ -1417,7 +1442,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1576,6 +1601,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Apriva 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 20 tablets</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-881A3558E0CC</t>
         </is>
       </c>
@@ -1599,7 +1629,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1758,6 +1788,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Zencin</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-00DADC5F3109</t>
         </is>
       </c>
@@ -1781,7 +1816,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1940,6 +1975,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Zencin</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-3C040D65ADF4</t>
         </is>
       </c>
@@ -1963,7 +2003,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2136,6 +2176,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Zersa</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-AB9F4E40E566</t>
         </is>
       </c>
@@ -2159,7 +2204,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2318,6 +2363,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>Rosalus 20mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-D86D383D570E</t>
         </is>
       </c>
@@ -2341,7 +2391,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2504,6 +2554,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Rosalus 10 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-C51164AC3131</t>
         </is>
       </c>
@@ -2527,7 +2582,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2690,6 +2745,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Rosalus 5 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-3D5ED54692BB</t>
         </is>
       </c>
@@ -2713,7 +2773,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2876,6 +2936,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Olcontro Plus</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-5DA63F36EAAC</t>
         </is>
       </c>
@@ -2899,7 +2964,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3062,6 +3127,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Olcontro Plus</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-1FA6345EEF1C</t>
         </is>
       </c>
@@ -3085,7 +3155,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3248,6 +3318,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>Ragilin</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-6DA25293981F</t>
         </is>
       </c>
@@ -3271,7 +3346,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3430,6 +3505,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Marixino</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-6FA48CB2936A</t>
         </is>
       </c>
@@ -3453,7 +3533,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3616,6 +3696,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>Feromenta Folic</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-6D5FFABDF2E8</t>
         </is>
       </c>
@@ -3639,7 +3724,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3794,6 +3879,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>Feromenta</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-124667D55A4C</t>
         </is>
       </c>
@@ -3817,7 +3907,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3980,6 +4070,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Quetal 400mg XR Tablets</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-85456531D22E</t>
         </is>
       </c>
@@ -4003,7 +4098,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4166,6 +4261,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>TiboFem</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-9555B121032E</t>
         </is>
       </c>
@@ -4189,7 +4289,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4360,6 +4460,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>Omnicef 250mg/5ml Suspension</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-F8E0B1F5E92F</t>
         </is>
       </c>
@@ -4383,7 +4488,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4542,6 +4647,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>Batlor</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-A653FCBD54D9</t>
         </is>
       </c>
@@ -4565,7 +4675,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4728,6 +4838,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>TALYNTA</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-A157C11E85E5</t>
         </is>
       </c>
@@ -4751,7 +4866,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4914,6 +5029,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>TALYNTA</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-87B87A1A249F</t>
         </is>
       </c>
@@ -4937,7 +5057,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5096,6 +5216,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Lorius</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-4F3A8DA0204B</t>
         </is>
       </c>
@@ -5119,7 +5244,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5278,6 +5403,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Lorius</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-6DAD8E1DECF6</t>
         </is>
       </c>
@@ -5301,7 +5431,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5460,6 +5590,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Zoxta</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-10935371E48C</t>
         </is>
       </c>
@@ -5483,7 +5618,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5646,6 +5781,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Zoxta</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-7D813447ACC6</t>
         </is>
       </c>
@@ -5669,7 +5809,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5828,6 +5968,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Dandaxa</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-853F4D5BE0B5</t>
         </is>
       </c>
@@ -5851,7 +5996,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6006,6 +6151,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>NEGAZOLE</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-93688C732931</t>
         </is>
       </c>
@@ -6029,7 +6179,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6188,6 +6338,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t xml:space="preserve">CLARIDAR XL 500 mg Tablet	</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-32A5697AF51F</t>
         </is>
       </c>
@@ -6211,7 +6366,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6390,6 +6545,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Glucophage XR</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-D0F70D0C2FC5</t>
         </is>
       </c>
@@ -6413,7 +6573,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6584,6 +6744,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Carbimazole Macleods</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-41154B4F2B98</t>
         </is>
       </c>
@@ -6607,7 +6772,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6780,6 +6945,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Keroz</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-C296CD8B54CB</t>
         </is>
       </c>
@@ -6803,7 +6973,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6970,6 +7140,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Neulasta Onpro</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-577D3CFFF65C</t>
         </is>
       </c>
@@ -6993,7 +7168,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7152,6 +7327,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>TRUMENBA</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-FAF16E3F345C</t>
         </is>
       </c>
@@ -7175,7 +7355,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7338,6 +7518,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Feromenta</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-B098B87EDA91</t>
         </is>
       </c>
@@ -7361,7 +7546,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7526,6 +7711,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Tedalix</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-1DE5B2229788</t>
         </is>
       </c>
@@ -7549,7 +7739,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7720,6 +7910,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Gizlan HCT</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-876A54E3AE3D</t>
         </is>
       </c>
@@ -7743,7 +7938,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7910,6 +8105,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Kesimpta</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-663C4BF1DDCF</t>
         </is>
       </c>
@@ -7933,7 +8133,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8104,6 +8304,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Virad</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-5017C89920AE</t>
         </is>
       </c>
@@ -8127,7 +8332,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8306,6 +8511,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Trivira</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-8F3AA879DF7B</t>
         </is>
       </c>
@@ -8329,7 +8539,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8500,6 +8710,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Oselow</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-6728224969D9</t>
         </is>
       </c>
@@ -8523,7 +8738,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8682,6 +8897,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Bosfit</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-58364F87FA39</t>
         </is>
       </c>
@@ -8705,7 +8925,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8876,6 +9096,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitram Film-Coated Tablet </t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-B12015E70AD6</t>
         </is>
       </c>
@@ -8899,7 +9124,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9058,6 +9283,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Quetta XR</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-BF3A0BEF3B98</t>
         </is>
       </c>
@@ -9081,7 +9311,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9248,6 +9478,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>IROREST FCT</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-823B5EC5F4D0</t>
         </is>
       </c>
@@ -9271,7 +9506,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9438,6 +9673,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>IROREST FCT</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-FD3B3E19EDB5</t>
         </is>
       </c>
@@ -9461,7 +9701,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9624,6 +9864,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Finate</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-EC4A6E051E51</t>
         </is>
       </c>
@@ -9647,7 +9892,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9810,6 +10055,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Cincet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-A720681375C1</t>
         </is>
       </c>
@@ -9833,7 +10083,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9996,6 +10246,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Cincet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-1020BFAA4D2B</t>
         </is>
       </c>
@@ -10019,7 +10274,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10178,6 +10433,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Veval</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-186455B35A39</t>
         </is>
       </c>
@@ -10201,7 +10461,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10360,6 +10620,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>Veval</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-61E47CF5DC28</t>
         </is>
       </c>
@@ -10383,7 +10648,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10542,6 +10807,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Urago</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-E0E55FDD8190</t>
         </is>
       </c>
@@ -10565,7 +10835,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10724,6 +10994,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Urago</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-693CEC6A58A8</t>
         </is>
       </c>
@@ -10747,7 +11022,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10910,6 +11185,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Lindacil</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-D900F613710B</t>
         </is>
       </c>
@@ -10933,7 +11213,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11100,6 +11380,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Lindacil</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-DB53D83071B8</t>
         </is>
       </c>
@@ -11123,7 +11408,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11282,6 +11567,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Iylus</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-80A6B7000FF7</t>
         </is>
       </c>
@@ -11305,7 +11595,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11472,6 +11762,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Zostivr</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-93B16CA9E692</t>
         </is>
       </c>
@@ -11495,7 +11790,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11662,6 +11957,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Divira</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-F09552D984F3</t>
         </is>
       </c>
@@ -11685,7 +11985,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11842,6 +12142,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Mavilor</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-A1C2C2F1A698</t>
         </is>
       </c>
@@ -11865,7 +12170,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12036,6 +12341,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>FLORATIL</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-CDBAA7032D7B</t>
         </is>
       </c>
@@ -12059,7 +12369,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12234,6 +12544,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>FLORATIL</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-CC5C3F1CAE29</t>
         </is>
       </c>
@@ -12257,7 +12572,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12424,6 +12739,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>NEURODERM</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-70D6BE236D4D</t>
         </is>
       </c>
@@ -12447,7 +12767,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12610,6 +12930,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>NERVAX 75MG CAPSULES 60 capsule</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-84EE39835572</t>
         </is>
       </c>
@@ -12633,7 +12958,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12796,6 +13121,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRILINTA 60 MG FILM COATED TABLET	</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-B7A1C2E97E50</t>
         </is>
       </c>
@@ -12819,7 +13149,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12990,6 +13320,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Pergoveris</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-76CFA87601D6</t>
         </is>
       </c>
@@ -13013,7 +13348,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13192,6 +13527,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>Pergoveris</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-6B51442F9D89</t>
         </is>
       </c>
@@ -13215,7 +13555,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13386,6 +13726,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Levozal</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-B893C0BB8E88</t>
         </is>
       </c>
@@ -13409,7 +13754,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13570,6 +13915,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>PXIDONE 1MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-CC7B243AA037</t>
         </is>
       </c>
@@ -13593,7 +13943,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13746,6 +14096,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>PXIDONE 2MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-3C94C4BF620A</t>
         </is>
       </c>
@@ -13769,7 +14124,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13930,6 +14285,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>PXIDONE 3MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-8005A8171942</t>
         </is>
       </c>
@@ -13953,7 +14313,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14114,6 +14474,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>PXIDONE 4MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-342A7AF5C930</t>
         </is>
       </c>
@@ -14137,7 +14502,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14298,6 +14663,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Erastapecs Plus 20/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-F7D6F446B977</t>
         </is>
       </c>
@@ -14321,7 +14691,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14474,6 +14844,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Erastapecs Plus 40/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-7B44B6CA7777</t>
         </is>
       </c>
@@ -14497,7 +14872,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14672,6 +15047,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Concor Amlo</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-2F7D11F2C901</t>
         </is>
       </c>
@@ -14695,7 +15075,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14874,6 +15254,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Concor Amlo</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-B5F7B00DC8D3</t>
         </is>
       </c>
@@ -14897,7 +15282,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15068,6 +15453,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Levozyrt</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-9EEFEED82065</t>
         </is>
       </c>
@@ -15091,7 +15481,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15258,6 +15648,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Trioltan</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-21721F87F620</t>
         </is>
       </c>
@@ -15281,7 +15676,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15448,6 +15843,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>Trioltan</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-D54A519B39C3</t>
         </is>
       </c>
@@ -15471,7 +15871,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15638,6 +16038,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Fulphila</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-076E9F512625</t>
         </is>
       </c>
@@ -15661,7 +16066,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15824,6 +16229,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>PRENA 15MG/5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-69210A600D91</t>
         </is>
       </c>
@@ -15847,7 +16257,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16010,6 +16420,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Zostivr</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-6ECEBE24B2FA</t>
         </is>
       </c>
@@ -16033,7 +16448,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16204,6 +16619,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ANTINAL  200 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-9C6F247F56FD</t>
         </is>
       </c>
@@ -16227,7 +16647,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16390,6 +16810,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Pedovex</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-3B0ADA779186</t>
         </is>
       </c>
@@ -16413,7 +16838,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16572,6 +16997,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Qualcox</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-5C79EF528A14</t>
         </is>
       </c>
@@ -16595,7 +17025,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16758,6 +17188,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Darista</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-342A9E5C2BFD</t>
         </is>
       </c>
@@ -16781,7 +17216,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16944,6 +17379,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Darista</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-2845D631404D</t>
         </is>
       </c>
@@ -16967,7 +17407,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17126,6 +17566,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Kalmo</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-50E1D87A4E57</t>
         </is>
       </c>
@@ -17149,7 +17594,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17316,6 +17761,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Pexapan</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-21F5909FD765</t>
         </is>
       </c>
@@ -17339,7 +17789,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17506,6 +17956,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Pexapan</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-3AD0D612936E</t>
         </is>
       </c>
@@ -17529,7 +17984,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17688,6 +18143,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Pexapan</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-98F61B2D2F93</t>
         </is>
       </c>
@@ -17711,7 +18171,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17884,6 +18344,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Relexib</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-8E783C00FF05</t>
         </is>
       </c>
@@ -17907,7 +18372,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18072,6 +18537,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Relexib</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-8445A10373F4</t>
         </is>
       </c>
@@ -18095,7 +18565,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18258,6 +18728,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Migrotan</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-09FB855126D0</t>
         </is>
       </c>
@@ -18281,7 +18756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18448,6 +18923,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Migrotan</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-9D93D999A6AE</t>
         </is>
       </c>
@@ -18471,7 +18951,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18638,6 +19118,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Resilia</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-F11F73BA13D4</t>
         </is>
       </c>
@@ -18661,7 +19146,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18828,6 +19313,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Resilia</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-0303F6067EBB</t>
         </is>
       </c>
@@ -18851,7 +19341,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19024,6 +19514,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Hivera</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-869B89BED48B</t>
         </is>
       </c>
@@ -19047,7 +19542,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19218,6 +19713,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>VFEND 40MG/ML POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-A244763A8501</t>
         </is>
       </c>
@@ -19241,7 +19741,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19401,6 +19901,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Starkoprex</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-900715AE41C0</t>
         </is>
@@ -19417,7 +19922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19463,100 +19968,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19588,7 +20098,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19603,92 +20113,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-71657</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>242.93</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>452</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19720,7 +20235,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19735,92 +20250,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-37564</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>225.44</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>453</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19852,7 +20372,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19867,92 +20387,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-65814</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>428.5</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>454</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19984,7 +20509,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19999,92 +20524,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-25446</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>467.43</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>455</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20116,7 +20646,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20131,92 +20661,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-22219</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>102.92</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>456</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20248,7 +20783,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20263,92 +20798,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-47796</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>332.42</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>457</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20380,7 +20920,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20395,92 +20935,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-25533</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>18.5</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>458</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20512,7 +21057,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20527,92 +21072,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-48295</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>318.84</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>459</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20644,7 +21194,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20659,92 +21209,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-41959</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>195.82</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>460</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20776,7 +21331,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20791,92 +21346,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-17162</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>300.76</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>461</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20908,7 +21468,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20923,92 +21483,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-15623</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>78.39</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>462</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21025,7 +21590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21131,6 +21696,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21166,7 +21741,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21231,6 +21806,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-993575D9AB7E</t>
         </is>
@@ -21267,7 +21852,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21332,6 +21917,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-4CA5E88C7728</t>
         </is>
@@ -21368,7 +21963,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21433,6 +22028,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-33462EB2E6CD</t>
         </is>
@@ -21469,7 +22074,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21534,6 +22139,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-A233D60B6ADA</t>
         </is>
@@ -21570,7 +22185,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21635,6 +22250,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-09714E3A1689</t>
         </is>
@@ -21671,7 +22296,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21736,6 +22361,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-B6C8AC47F6D1</t>
         </is>
@@ -21772,7 +22407,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21837,6 +22472,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-837D2CED96DB</t>
         </is>
@@ -21873,7 +22518,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21938,6 +22583,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-874122E32B86</t>
         </is>
@@ -21974,7 +22629,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22039,6 +22694,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-F21363E66F23</t>
         </is>
@@ -22075,7 +22740,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22140,6 +22805,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-2CCA080DA893</t>
         </is>
@@ -22176,7 +22851,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22241,6 +22916,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-8A3574779B97</t>
         </is>
@@ -22277,7 +22962,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22342,6 +23027,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-1683B044F740</t>
         </is>
@@ -22378,7 +23073,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22443,6 +23138,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-1C1532D77FFF</t>
         </is>
@@ -22479,7 +23184,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22544,6 +23249,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-18E94CF0EFD3</t>
         </is>
@@ -22580,7 +23295,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22645,6 +23360,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-0BBAA36C5B26</t>
         </is>
@@ -22681,7 +23406,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22746,6 +23471,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-46FE5517646C</t>
         </is>
@@ -22782,7 +23517,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22847,6 +23582,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-70BC02C680DC</t>
         </is>
@@ -22883,7 +23628,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22948,6 +23693,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-027BDB24E87C</t>
         </is>
@@ -22984,7 +23739,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23049,6 +23804,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-5F4649718708</t>
         </is>
@@ -23085,7 +23850,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23150,6 +23915,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-9A245A2D7355</t>
         </is>

--- a/product_upload/packages/48/file.xlsx
+++ b/product_upload/packages/48/file.xlsx
@@ -686,8 +686,16 @@
           <t>4162806536-713-892204755767</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sayen</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sayen detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -873,8 +881,16 @@
           <t>1878499740-555-533862914469</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sayen</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sayen detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1259,8 +1275,16 @@
           <t>5009846555-764-434310886435</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apriva</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Apriva detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1450,8 +1474,16 @@
           <t>0545104337-597-475561654162</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apriva 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 20 tablets</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Apriva 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 20 tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1637,8 +1669,16 @@
           <t>7332591733-073-889041727780</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zencin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Zencin detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1824,8 +1864,16 @@
           <t>9567331544-677-547751733804</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zencin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Zencin detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2212,8 +2260,16 @@
           <t>4837974505-518-297323825034</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosalus 20mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rosalus 20mg Film coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2399,8 +2455,16 @@
           <t>4270628693-516-822526776065</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosalus 10 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rosalus 10 mg Film Coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2590,8 +2654,16 @@
           <t>3202309180-728-112048195910</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosalus 5 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rosalus 5 mg Film Coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2781,8 +2853,16 @@
           <t>9055291885-362-328093343428</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olcontro Plus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Olcontro Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2972,8 +3052,16 @@
           <t>9374448793-522-168841000844</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olcontro Plus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Olcontro Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3163,8 +3251,16 @@
           <t>5910544507-317-879620724462</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ragilin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ragilin detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3354,8 +3450,16 @@
           <t>6689943777-293-747316923409</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Marixino</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Marixino detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3541,8 +3645,16 @@
           <t>2110048612-182-732043415170</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Feromenta Folic</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Feromenta Folic detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3732,8 +3844,16 @@
           <t>2819542761-357-904233382053</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Feromenta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Feromenta detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3915,8 +4035,16 @@
           <t>8471765608-267-256247404814</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Quetal 400mg XR Tablets</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Quetal 400mg XR Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4106,8 +4234,16 @@
           <t>3930326209-311-356543172595</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TiboFem</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TiboFem detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4496,8 +4632,16 @@
           <t>1180229793-139-191818314718</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Batlor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Batlor detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4683,8 +4827,16 @@
           <t>7036820510-217-120436731629</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TALYNTA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TALYNTA detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4874,8 +5026,16 @@
           <t>7943443779-810-078908312189</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TALYNTA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TALYNTA detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5065,8 +5225,16 @@
           <t>5013348718-476-236227057807</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lorius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Lorius detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5252,8 +5420,16 @@
           <t>1351090169-247-996641338037</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lorius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Lorius detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5439,8 +5615,16 @@
           <t>7553185867-013-743466701709</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zoxta</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Zoxta detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5626,8 +5810,16 @@
           <t>5145426782-472-758263294158</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zoxta</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Zoxta detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5817,8 +6009,16 @@
           <t>2026528195-180-371877711833</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dandaxa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Dandaxa detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6004,8 +6204,16 @@
           <t>4619687457-399-813698512044</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEGAZOLE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NEGAZOLE detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6187,8 +6395,16 @@
           <t>0048735575-915-069570703869</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARIDAR XL 500 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CLARIDAR XL 500 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6981,8 +7197,16 @@
           <t>7244496305-875-423006903044</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Neulasta Onpro</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Neulasta Onpro detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7176,8 +7400,16 @@
           <t>2003511022-191-270542131388</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRUMENBA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TRUMENBA detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7363,8 +7595,16 @@
           <t>6088958944-243-847767135788</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Feromenta</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Feromenta detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7554,8 +7794,16 @@
           <t>5675869277-543-581508294617</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tedalix</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tedalix detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -8746,8 +8994,16 @@
           <t>5699655196-368-143445906991</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bosfit</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bosfit detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9132,8 +9388,16 @@
           <t>2563985178-638-752250034503</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Quetta XR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Quetta XR detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9709,8 +9973,16 @@
           <t>3007526676-979-809813097192</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Finate</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Finate detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9900,8 +10172,16 @@
           <t>3058126102-761-738501654084</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cincet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Cincet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10091,8 +10371,16 @@
           <t>1588130452-168-309177809176</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cincet</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Cincet detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10282,8 +10570,16 @@
           <t>9155089992-957-213675747585</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Veval</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Veval detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10469,8 +10765,16 @@
           <t>0113501561-063-685532507003</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Veval</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Veval detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10656,8 +10960,16 @@
           <t>2678647965-335-578230581653</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Urago</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Urago detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10843,8 +11155,16 @@
           <t>8234464111-211-299389183203</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Urago</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Urago detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11416,8 +11736,16 @@
           <t>7385991231-283-037585105859</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Iylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Iylus detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11603,8 +11931,16 @@
           <t>5425573981-735-202910703343</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zostivr</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Zostivr detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11798,8 +12134,16 @@
           <t>7589138769-575-094654763878</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Divira</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Divira detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11993,8 +12337,16 @@
           <t>9028273038-617-372583140484</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mavilor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Mavilor detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -12580,8 +12932,16 @@
           <t>6945758373-133-677894041369</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEURODERM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NEURODERM detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12775,8 +13135,16 @@
           <t>8943246257-722-373148565901</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NERVAX 75MG CAPSULES 60 capsule</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NERVAX 75MG CAPSULES 60 capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12966,8 +13334,16 @@
           <t>7260513275-051-123891566298</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRILINTA 60 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BRILINTA 60 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13762,8 +14138,16 @@
           <t>2788662902-891-551710988910</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PXIDONE 1MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PXIDONE 1MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -13951,8 +14335,16 @@
           <t>9544991625-197-745204089864</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PXIDONE 2MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>PXIDONE 2MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -14132,8 +14524,16 @@
           <t>5977954971-628-046153362124</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PXIDONE 3MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>PXIDONE 3MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -14321,8 +14721,16 @@
           <t>5368529230-310-536603907235</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PXIDONE 4MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>PXIDONE 4MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -14510,8 +14918,16 @@
           <t>0274705499-756-626843794388</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Plus 20/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Erastapecs Plus 20/12.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -14699,8 +15115,16 @@
           <t>3966239432-663-202996883243</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Plus 40/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Erastapecs Plus 40/12.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -15489,8 +15913,16 @@
           <t>8415188810-696-517549265817</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trioltan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Trioltan detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15684,8 +16116,16 @@
           <t>4263626606-604-511141272347</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trioltan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Trioltan detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15879,8 +16319,16 @@
           <t>5936089917-429-613113660842</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fulphila</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Fulphila detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16074,8 +16522,16 @@
           <t>2220324344-899-743251619585</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRENA 15MG/5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PRENA 15MG/5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16265,8 +16721,16 @@
           <t>0638094165-489-551120936104</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zostivr</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Zostivr detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16846,8 +17310,16 @@
           <t>6715709738-062-266400806196</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Qualcox</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Qualcox detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17033,8 +17505,16 @@
           <t>9773248077-622-637677761753</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Darista</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Darista detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17224,8 +17704,16 @@
           <t>6799724771-613-864392358135</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Darista</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Darista detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17415,8 +17903,16 @@
           <t>5795361140-076-814053594215</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Kalmo</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kalmo detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17992,8 +18488,16 @@
           <t>5693916985-318-198147829302</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pexapan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Pexapan detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18380,8 +18884,16 @@
           <t>4013847880-664-032300869576</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Relexib</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Relexib detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
@@ -19550,8 +20062,16 @@
           <t>0575678651-377-483443248854</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VFEND 40MG/ML POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>VFEND 40MG/ML POWDER FOR SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19749,8 +20269,16 @@
           <t>4279654744-583-318515596025</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Starkoprex</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Starkoprex detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>

--- a/product_upload/packages/48/file.xlsx
+++ b/product_upload/packages/48/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22118,7 +22118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22199,40 +22199,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22312,38 +22317,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>413.81</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-993575D9AB7E</t>
         </is>
@@ -22423,38 +22433,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>82.55</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-4CA5E88C7728</t>
         </is>
@@ -22534,38 +22549,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>392.35</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-33462EB2E6CD</t>
         </is>
@@ -22645,38 +22665,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>133.73</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-A233D60B6ADA</t>
         </is>
@@ -22756,38 +22781,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>33.49</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-09714E3A1689</t>
         </is>
@@ -22867,38 +22897,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>214</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-B6C8AC47F6D1</t>
         </is>
@@ -22978,38 +23013,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>227.58</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-837D2CED96DB</t>
         </is>
@@ -23089,38 +23129,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>482.17</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-874122E32B86</t>
         </is>
@@ -23200,38 +23245,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>131.43</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-F21363E66F23</t>
         </is>
@@ -23311,38 +23361,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>395.35</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-2CCA080DA893</t>
         </is>
@@ -23422,38 +23477,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>14.91</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-8A3574779B97</t>
         </is>
@@ -23533,38 +23593,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>93.59</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-1683B044F740</t>
         </is>
@@ -23644,38 +23709,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>452.2</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-1C1532D77FFF</t>
         </is>
@@ -23755,38 +23825,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>316.4</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-18E94CF0EFD3</t>
         </is>
@@ -23866,38 +23941,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>154.25</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-0BBAA36C5B26</t>
         </is>
@@ -23977,38 +24057,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>173.23</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-46FE5517646C</t>
         </is>
@@ -24088,38 +24173,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>319.95</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-70BC02C680DC</t>
         </is>
@@ -24199,38 +24289,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>141.18</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-027BDB24E87C</t>
         </is>
@@ -24310,38 +24405,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>14.2</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-5F4649718708</t>
         </is>
@@ -24421,38 +24521,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>272.91</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-9A245A2D7355</t>
         </is>
